--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/0051-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/0051-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B66F96A8-E0BF-4C03-BCD8-14C693795A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1A1DB11-B23B-41F4-A21A-BE18F3FF3680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{56221C18-9255-49C1-B206-6EF473F70C32}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{458BD93C-BE5E-48A6-9D02-948E0E2F2241}"/>
   </bookViews>
   <sheets>
     <sheet name="0051-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1463,29 +1463,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BFD393D-589C-463F-93D9-B32B0716FEB9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9027D9F0-DAC0-4149-A588-3851F6135150}">
   <dimension ref="A1:X24"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="4" width="6.625" customWidth="1"/>
-    <col min="5" max="5" width="6.25" customWidth="1"/>
-    <col min="6" max="6" width="6.625" customWidth="1"/>
-    <col min="7" max="9" width="6.25" customWidth="1"/>
-    <col min="10" max="10" width="6.625" customWidth="1"/>
-    <col min="11" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="14" width="6.625" customWidth="1"/>
-    <col min="15" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1519,7 +1518,7 @@
       <c r="W1" s="26"/>
       <c r="X1" s="18"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1555,7 +1554,7 @@
       <c r="W2" s="28"/>
       <c r="X2" s="29"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1607,7 +1606,7 @@
       </c>
       <c r="X3" s="32"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1675,7 +1674,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>2024</v>
       </c>
@@ -1747,7 +1746,7 @@
         <v>5.23</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>2023</v>
       </c>
@@ -1819,7 +1818,7 @@
         <v>3.47</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>2022</v>
       </c>
@@ -1891,7 +1890,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>2021</v>
       </c>
@@ -1963,7 +1962,7 @@
         <v>4.99</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>2020</v>
       </c>
@@ -2035,7 +2034,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2019</v>
       </c>
@@ -2107,7 +2106,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
         <v>2018</v>
       </c>
@@ -2179,7 +2178,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2017</v>
       </c>
@@ -2251,7 +2250,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>2016</v>
       </c>
@@ -2323,7 +2322,7 @@
         <v>3.34</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2015</v>
       </c>
@@ -2395,7 +2394,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="33">
         <v>2014</v>
       </c>
@@ -2467,7 +2466,7 @@
         <v>3.82</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2013</v>
       </c>
@@ -2539,7 +2538,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
         <v>2012</v>
       </c>
@@ -2611,7 +2610,7 @@
         <v>3.14</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2011</v>
       </c>
@@ -2683,7 +2682,7 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="33">
         <v>2010</v>
       </c>
@@ -2755,7 +2754,7 @@
         <v>4.1399999999999997</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2009</v>
       </c>
@@ -2827,7 +2826,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="33">
         <v>2008</v>
       </c>
@@ -2899,7 +2898,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2007</v>
       </c>
@@ -2971,7 +2970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="33">
         <v>2006</v>
       </c>
@@ -3043,7 +3042,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35" t="s">
         <v>47</v>
       </c>
